--- a/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>

--- a/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>listed-building-grade-known</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Listed building grade known</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4206,12 +4206,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Set to true if the applicant knows the listed building grade. Set to false if they do not know it.</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4246,17 +4246,17 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4286,12 +4286,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4301,29 +4301,21 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4334,23 +4326,31 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Planning officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4374,17 +4374,17 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4454,12 +4454,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4494,12 +4494,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4509,64 +4509,56 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>geometry</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>A polygon or multipolygon boundary</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>multipolygon</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4584,34 +4576,26 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>site-address</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site boundary</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4650,19 +4634,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4706,19 +4690,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4762,19 +4746,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>usrns</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>USRNs[]</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4808,26 +4792,34 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4856,12 +4848,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4870,7 +4862,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4904,12 +4896,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4918,12 +4910,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4952,12 +4944,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4966,71 +4958,79 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>site-locations</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>can-be-seen-from</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -5054,12 +5054,12 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -5094,17 +5094,17 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5118,31 +5118,23 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -5152,7 +5144,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5168,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -5190,7 +5182,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -5224,12 +5216,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -5238,15 +5230,63 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5256,34 +5296,34 @@
   <mergeCells count="30">
     <mergeCell ref="B49"/>
     <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B78:B86"/>
     <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A69:A72"/>
     <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A72:A76"/>
     <mergeCell ref="A44"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="B45"/>
     <mergeCell ref="B52:B68"/>
-    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="A87:A92"/>
     <mergeCell ref="A49"/>
     <mergeCell ref="B24:B32"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="A73:A77"/>
     <mergeCell ref="A45"/>
-    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="B87:B92"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A77:A85"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="B33:B36"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B44"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A78:A86"/>
+    <mergeCell ref="B73:B77"/>
     <mergeCell ref="A52:A68"/>
     <mergeCell ref="B2:B19"/>
     <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B69:B71"/>
     <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B77:B85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
